--- a/docs/sap490/generated/Test_Scenario_IDTS_SAP01_vi_v0.3.xlsx
+++ b/docs/sap490/generated/Test_Scenario_IDTS_SAP01_vi_v0.3.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="181">
   <si>
     <t xml:space="preserve">Kịch bản kiểm thử</t>
   </si>
@@ -468,7 +468,11 @@
     <t xml:space="preserve">FUNCTIONAL_UI_API / POSITIVE_NEGATIVE / HIGH</t>
   </si>
   <si>
-    <t xml:space="preserve">NOT_RUN</t>
+    <t xml:space="preserve">IDTS-100 automated acceptance under DonHV
+2026-07-24T20:42:48+07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docs/pm/evidence/idts-100/shared-qa-ai/render-ai-smoke.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/all-review-actions/shared-qa-ai-browser.json</t>
   </si>
   <si>
     <t xml:space="preserve">Phân loại và assign theo responsibility active
@@ -488,7 +492,8 @@
     <t xml:space="preserve">FUNCTIONAL_UI_API / POSITIVE_BOUNDARY / HIGH</t>
   </si>
   <si>
-    <t xml:space="preserve">IDTS-56</t>
+    <t xml:space="preserve">docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/assignment/idts72-ai-browser-smoke.json
+IDTS-56</t>
   </si>
   <si>
     <t xml:space="preserve">Tạo bug không có assignee
@@ -508,6 +513,9 @@
     <t xml:space="preserve">FUNCTIONAL_UI_API / BOUNDARY / HIGH</t>
   </si>
   <si>
+    <t xml:space="preserve">docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reassign có history
 Mục tiêu: Xác minh reassign có quyền thay một technical owner và ghi history.
 Req: SRS-FR-ASSIGN-004, SRS-FR-AUDIT-001
@@ -542,6 +550,9 @@
     <t xml:space="preserve">FUNCTIONAL_UI_API / POSITIVE_NEGATIVE_AUTHORIZATION / HIGH</t>
   </si>
   <si>
+    <t xml:space="preserve">docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json, docs/pm/evidence/idts-100/shared-qa-email-brevo-20260724.md</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reject, sửa và reassign
 Mục tiêu: Xác minh rejection không phải terminal và cần reason cùng follow-up owner.
 Req: SRS-FR-STATUS-003, SRS-FR-STATUS-004, SRS-FR-STATUS-009
@@ -612,7 +623,7 @@
     <t xml:space="preserve">FUNCTIONAL_HTTP_UI / POSITIVE_NEGATIVE_PERSISTENCE / HIGH</t>
   </si>
   <si>
-    <t xml:space="preserve">scripts/qa/test-comments-attachments.ps1
+    <t xml:space="preserve">docs/pm/evidence/idts-100/shared-qa-attachments/idts73-create-attachments-browser.json, docs/pm/evidence/idts-100/shared-qa-attachments/delete-verification-20260724.md
 IDTS-55</t>
   </si>
   <si>
@@ -681,7 +692,8 @@
     <t xml:space="preserve">FUNCTIONAL_UI_API / POSITIVE_NEGATIVE_FAILURE_RECOVERY / HIGH</t>
   </si>
   <si>
-    <t xml:space="preserve">IDTS-78</t>
+    <t xml:space="preserve">docs/pm/evidence/idts-100/shared-qa-ai/render-ai-smoke.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/all-review-actions/shared-qa-ai-browser.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/assignment/idts72-ai-browser-smoke.json
+IDTS-78</t>
   </si>
 </sst>
 </file>
@@ -7923,17 +7935,21 @@
       <c r="BR17" s="75"/>
       <c r="BS17" s="75"/>
       <c r="BT17" s="75"/>
-      <c r="BU17" s="76"/>
+      <c r="BU17" s="76" t="s">
+        <v>126</v>
+      </c>
       <c r="BV17" s="76"/>
       <c r="BW17" s="76"/>
       <c r="BX17" s="76"/>
       <c r="BY17" s="76"/>
       <c r="BZ17" s="76"/>
       <c r="CA17" s="69" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="CB17" s="69"/>
-      <c r="CC17" s="77"/>
+      <c r="CC17" s="77" t="s">
+        <v>127</v>
+      </c>
       <c r="CD17" s="77"/>
       <c r="CE17" s="77"/>
       <c r="CF17" s="77"/>
@@ -7949,7 +7965,7 @@
       <c r="C18" s="79"/>
       <c r="D18" s="79"/>
       <c r="E18" s="74" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F18" s="74"/>
       <c r="G18" s="74"/>
@@ -7971,7 +7987,7 @@
       <c r="W18" s="74"/>
       <c r="X18" s="74"/>
       <c r="Y18" s="73" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Z18" s="73"/>
       <c r="AA18" s="73"/>
@@ -7990,7 +8006,7 @@
       <c r="AN18" s="73"/>
       <c r="AO18" s="73"/>
       <c r="AP18" s="74" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AQ18" s="74"/>
       <c r="AR18" s="74"/>
@@ -8017,25 +8033,27 @@
       <c r="BM18" s="74"/>
       <c r="BN18" s="74"/>
       <c r="BO18" s="75" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BP18" s="75"/>
       <c r="BQ18" s="75"/>
       <c r="BR18" s="75"/>
       <c r="BS18" s="75"/>
       <c r="BT18" s="75"/>
-      <c r="BU18" s="76"/>
+      <c r="BU18" s="76" t="s">
+        <v>126</v>
+      </c>
       <c r="BV18" s="76"/>
       <c r="BW18" s="76"/>
       <c r="BX18" s="76"/>
       <c r="BY18" s="76"/>
       <c r="BZ18" s="76"/>
       <c r="CA18" s="69" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="CB18" s="69"/>
       <c r="CC18" s="77" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="CD18" s="77"/>
       <c r="CE18" s="77"/>
@@ -8052,7 +8070,7 @@
       <c r="C19" s="71"/>
       <c r="D19" s="71"/>
       <c r="E19" s="72" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F19" s="72"/>
       <c r="G19" s="72"/>
@@ -8074,7 +8092,7 @@
       <c r="W19" s="72"/>
       <c r="X19" s="72"/>
       <c r="Y19" s="73" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Z19" s="73"/>
       <c r="AA19" s="73"/>
@@ -8093,7 +8111,7 @@
       <c r="AN19" s="73"/>
       <c r="AO19" s="73"/>
       <c r="AP19" s="74" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AQ19" s="74"/>
       <c r="AR19" s="74"/>
@@ -8120,24 +8138,28 @@
       <c r="BM19" s="74"/>
       <c r="BN19" s="74"/>
       <c r="BO19" s="75" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BP19" s="75"/>
       <c r="BQ19" s="75"/>
       <c r="BR19" s="75"/>
       <c r="BS19" s="75"/>
       <c r="BT19" s="75"/>
-      <c r="BU19" s="76"/>
+      <c r="BU19" s="76" t="s">
+        <v>126</v>
+      </c>
       <c r="BV19" s="76"/>
       <c r="BW19" s="76"/>
       <c r="BX19" s="76"/>
       <c r="BY19" s="76"/>
       <c r="BZ19" s="76"/>
       <c r="CA19" s="69" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="CB19" s="69"/>
-      <c r="CC19" s="77"/>
+      <c r="CC19" s="77" t="s">
+        <v>137</v>
+      </c>
       <c r="CD19" s="77"/>
       <c r="CE19" s="77"/>
       <c r="CF19" s="77"/>
@@ -8153,7 +8175,7 @@
       <c r="C20" s="79"/>
       <c r="D20" s="79"/>
       <c r="E20" s="74" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F20" s="74"/>
       <c r="G20" s="74"/>
@@ -8175,7 +8197,7 @@
       <c r="W20" s="74"/>
       <c r="X20" s="74"/>
       <c r="Y20" s="73" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Z20" s="73"/>
       <c r="AA20" s="73"/>
@@ -8194,7 +8216,7 @@
       <c r="AN20" s="73"/>
       <c r="AO20" s="73"/>
       <c r="AP20" s="74" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AQ20" s="74"/>
       <c r="AR20" s="74"/>
@@ -8221,24 +8243,28 @@
       <c r="BM20" s="74"/>
       <c r="BN20" s="74"/>
       <c r="BO20" s="75" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="BP20" s="75"/>
       <c r="BQ20" s="75"/>
       <c r="BR20" s="75"/>
       <c r="BS20" s="75"/>
       <c r="BT20" s="75"/>
-      <c r="BU20" s="76"/>
+      <c r="BU20" s="76" t="s">
+        <v>126</v>
+      </c>
       <c r="BV20" s="76"/>
       <c r="BW20" s="76"/>
       <c r="BX20" s="76"/>
       <c r="BY20" s="76"/>
       <c r="BZ20" s="76"/>
       <c r="CA20" s="69" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="CB20" s="69"/>
-      <c r="CC20" s="77"/>
+      <c r="CC20" s="77" t="s">
+        <v>137</v>
+      </c>
       <c r="CD20" s="77"/>
       <c r="CE20" s="77"/>
       <c r="CF20" s="77"/>
@@ -8254,7 +8280,7 @@
       <c r="C21" s="79"/>
       <c r="D21" s="79"/>
       <c r="E21" s="74" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F21" s="74"/>
       <c r="G21" s="74"/>
@@ -8276,7 +8302,7 @@
       <c r="W21" s="74"/>
       <c r="X21" s="74"/>
       <c r="Y21" s="73" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Z21" s="73"/>
       <c r="AA21" s="73"/>
@@ -8295,7 +8321,7 @@
       <c r="AN21" s="73"/>
       <c r="AO21" s="73"/>
       <c r="AP21" s="74" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AQ21" s="74"/>
       <c r="AR21" s="74"/>
@@ -8322,24 +8348,28 @@
       <c r="BM21" s="74"/>
       <c r="BN21" s="74"/>
       <c r="BO21" s="75" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BP21" s="75"/>
       <c r="BQ21" s="75"/>
       <c r="BR21" s="75"/>
       <c r="BS21" s="75"/>
       <c r="BT21" s="75"/>
-      <c r="BU21" s="76"/>
+      <c r="BU21" s="76" t="s">
+        <v>126</v>
+      </c>
       <c r="BV21" s="76"/>
       <c r="BW21" s="76"/>
       <c r="BX21" s="76"/>
       <c r="BY21" s="76"/>
       <c r="BZ21" s="76"/>
       <c r="CA21" s="69" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="CB21" s="69"/>
-      <c r="CC21" s="77"/>
+      <c r="CC21" s="77" t="s">
+        <v>146</v>
+      </c>
       <c r="CD21" s="77"/>
       <c r="CE21" s="77"/>
       <c r="CF21" s="77"/>
@@ -8355,7 +8385,7 @@
       <c r="C22" s="79"/>
       <c r="D22" s="79"/>
       <c r="E22" s="74" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F22" s="74"/>
       <c r="G22" s="74"/>
@@ -8377,7 +8407,7 @@
       <c r="W22" s="74"/>
       <c r="X22" s="74"/>
       <c r="Y22" s="73" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Z22" s="73"/>
       <c r="AA22" s="73"/>
@@ -8396,7 +8426,7 @@
       <c r="AN22" s="73"/>
       <c r="AO22" s="73"/>
       <c r="AP22" s="74" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AQ22" s="74"/>
       <c r="AR22" s="74"/>
@@ -8430,17 +8460,21 @@
       <c r="BR22" s="75"/>
       <c r="BS22" s="75"/>
       <c r="BT22" s="75"/>
-      <c r="BU22" s="76"/>
+      <c r="BU22" s="76" t="s">
+        <v>126</v>
+      </c>
       <c r="BV22" s="76"/>
       <c r="BW22" s="76"/>
       <c r="BX22" s="76"/>
       <c r="BY22" s="76"/>
       <c r="BZ22" s="76"/>
       <c r="CA22" s="69" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="CB22" s="69"/>
-      <c r="CC22" s="77"/>
+      <c r="CC22" s="77" t="s">
+        <v>146</v>
+      </c>
       <c r="CD22" s="77"/>
       <c r="CE22" s="77"/>
       <c r="CF22" s="77"/>
@@ -8456,7 +8490,7 @@
       <c r="C23" s="79"/>
       <c r="D23" s="79"/>
       <c r="E23" s="74" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F23" s="74"/>
       <c r="G23" s="74"/>
@@ -8478,7 +8512,7 @@
       <c r="W23" s="74"/>
       <c r="X23" s="74"/>
       <c r="Y23" s="73" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Z23" s="73"/>
       <c r="AA23" s="73"/>
@@ -8497,7 +8531,7 @@
       <c r="AN23" s="73"/>
       <c r="AO23" s="73"/>
       <c r="AP23" s="74" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AQ23" s="74"/>
       <c r="AR23" s="74"/>
@@ -8531,17 +8565,21 @@
       <c r="BR23" s="75"/>
       <c r="BS23" s="75"/>
       <c r="BT23" s="75"/>
-      <c r="BU23" s="76"/>
+      <c r="BU23" s="76" t="s">
+        <v>126</v>
+      </c>
       <c r="BV23" s="76"/>
       <c r="BW23" s="76"/>
       <c r="BX23" s="76"/>
       <c r="BY23" s="76"/>
       <c r="BZ23" s="76"/>
       <c r="CA23" s="69" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="CB23" s="69"/>
-      <c r="CC23" s="77"/>
+      <c r="CC23" s="77" t="s">
+        <v>146</v>
+      </c>
       <c r="CD23" s="77"/>
       <c r="CE23" s="77"/>
       <c r="CF23" s="77"/>
@@ -8557,7 +8595,7 @@
       <c r="C24" s="79"/>
       <c r="D24" s="79"/>
       <c r="E24" s="74" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F24" s="74"/>
       <c r="G24" s="74"/>
@@ -8579,7 +8617,7 @@
       <c r="W24" s="74"/>
       <c r="X24" s="74"/>
       <c r="Y24" s="73" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Z24" s="73"/>
       <c r="AA24" s="73"/>
@@ -8598,7 +8636,7 @@
       <c r="AN24" s="73"/>
       <c r="AO24" s="73"/>
       <c r="AP24" s="74" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AQ24" s="74"/>
       <c r="AR24" s="74"/>
@@ -8625,7 +8663,7 @@
       <c r="BM24" s="74"/>
       <c r="BN24" s="74"/>
       <c r="BO24" s="75" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="BP24" s="75"/>
       <c r="BQ24" s="75"/>
@@ -8633,7 +8671,7 @@
       <c r="BS24" s="75"/>
       <c r="BT24" s="75"/>
       <c r="BU24" s="76" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="BV24" s="76"/>
       <c r="BW24" s="76"/>
@@ -8645,7 +8683,7 @@
       </c>
       <c r="CB24" s="69"/>
       <c r="CC24" s="77" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="CD24" s="77"/>
       <c r="CE24" s="77"/>
@@ -8662,7 +8700,7 @@
       <c r="C25" s="71"/>
       <c r="D25" s="71"/>
       <c r="E25" s="72" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F25" s="72"/>
       <c r="G25" s="72"/>
@@ -8684,7 +8722,7 @@
       <c r="W25" s="72"/>
       <c r="X25" s="72"/>
       <c r="Y25" s="73" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Z25" s="73"/>
       <c r="AA25" s="73"/>
@@ -8703,7 +8741,7 @@
       <c r="AN25" s="73"/>
       <c r="AO25" s="73"/>
       <c r="AP25" s="74" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AQ25" s="74"/>
       <c r="AR25" s="74"/>
@@ -8730,25 +8768,27 @@
       <c r="BM25" s="74"/>
       <c r="BN25" s="74"/>
       <c r="BO25" s="75" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="BP25" s="75"/>
       <c r="BQ25" s="75"/>
       <c r="BR25" s="75"/>
       <c r="BS25" s="75"/>
       <c r="BT25" s="75"/>
-      <c r="BU25" s="76"/>
+      <c r="BU25" s="76" t="s">
+        <v>126</v>
+      </c>
       <c r="BV25" s="76"/>
       <c r="BW25" s="76"/>
       <c r="BX25" s="76"/>
       <c r="BY25" s="76"/>
       <c r="BZ25" s="76"/>
       <c r="CA25" s="69" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="CB25" s="69"/>
       <c r="CC25" s="77" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="CD25" s="77"/>
       <c r="CE25" s="77"/>
@@ -8765,7 +8805,7 @@
       <c r="C26" s="79"/>
       <c r="D26" s="79"/>
       <c r="E26" s="74" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F26" s="74"/>
       <c r="G26" s="74"/>
@@ -8787,7 +8827,7 @@
       <c r="W26" s="74"/>
       <c r="X26" s="74"/>
       <c r="Y26" s="73" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Z26" s="73"/>
       <c r="AA26" s="73"/>
@@ -8806,7 +8846,7 @@
       <c r="AN26" s="73"/>
       <c r="AO26" s="73"/>
       <c r="AP26" s="74" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AQ26" s="74"/>
       <c r="AR26" s="74"/>
@@ -8833,7 +8873,7 @@
       <c r="BM26" s="74"/>
       <c r="BN26" s="74"/>
       <c r="BO26" s="75" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="BP26" s="75"/>
       <c r="BQ26" s="75"/>
@@ -8841,7 +8881,7 @@
       <c r="BS26" s="75"/>
       <c r="BT26" s="75"/>
       <c r="BU26" s="76" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="BV26" s="76"/>
       <c r="BW26" s="76"/>
@@ -8853,7 +8893,7 @@
       </c>
       <c r="CB26" s="69"/>
       <c r="CC26" s="77" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="CD26" s="77"/>
       <c r="CE26" s="77"/>
@@ -8870,7 +8910,7 @@
       <c r="C27" s="79"/>
       <c r="D27" s="79"/>
       <c r="E27" s="74" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F27" s="74"/>
       <c r="G27" s="74"/>
@@ -8892,7 +8932,7 @@
       <c r="W27" s="74"/>
       <c r="X27" s="74"/>
       <c r="Y27" s="73" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Z27" s="73"/>
       <c r="AA27" s="73"/>
@@ -8911,7 +8951,7 @@
       <c r="AN27" s="73"/>
       <c r="AO27" s="73"/>
       <c r="AP27" s="74" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="AQ27" s="74"/>
       <c r="AR27" s="74"/>
@@ -8938,7 +8978,7 @@
       <c r="BM27" s="74"/>
       <c r="BN27" s="74"/>
       <c r="BO27" s="75" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="BP27" s="75"/>
       <c r="BQ27" s="75"/>
@@ -8946,7 +8986,7 @@
       <c r="BS27" s="75"/>
       <c r="BT27" s="75"/>
       <c r="BU27" s="76" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="BV27" s="76"/>
       <c r="BW27" s="76"/>
@@ -8958,7 +8998,7 @@
       </c>
       <c r="CB27" s="69"/>
       <c r="CC27" s="77" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="CD27" s="77"/>
       <c r="CE27" s="77"/>
@@ -8975,7 +9015,7 @@
       <c r="C28" s="79"/>
       <c r="D28" s="79"/>
       <c r="E28" s="74" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F28" s="74"/>
       <c r="G28" s="74"/>
@@ -8997,7 +9037,7 @@
       <c r="W28" s="74"/>
       <c r="X28" s="74"/>
       <c r="Y28" s="73" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Z28" s="73"/>
       <c r="AA28" s="73"/>
@@ -9016,7 +9056,7 @@
       <c r="AN28" s="73"/>
       <c r="AO28" s="73"/>
       <c r="AP28" s="74" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AQ28" s="74"/>
       <c r="AR28" s="74"/>
@@ -9043,25 +9083,27 @@
       <c r="BM28" s="74"/>
       <c r="BN28" s="74"/>
       <c r="BO28" s="75" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BP28" s="75"/>
       <c r="BQ28" s="75"/>
       <c r="BR28" s="75"/>
       <c r="BS28" s="75"/>
       <c r="BT28" s="75"/>
-      <c r="BU28" s="76"/>
+      <c r="BU28" s="76" t="s">
+        <v>126</v>
+      </c>
       <c r="BV28" s="76"/>
       <c r="BW28" s="76"/>
       <c r="BX28" s="76"/>
       <c r="BY28" s="76"/>
       <c r="BZ28" s="76"/>
       <c r="CA28" s="69" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="CB28" s="69"/>
       <c r="CC28" s="77" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="CD28" s="77"/>
       <c r="CE28" s="77"/>
